--- a/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre</t>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,82</t>
+          <t>0,0; 26,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 55,64</t>
+          <t>14,78; 55,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 35,4</t>
+          <t>7,63; 35,74</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,54</t>
+          <t>5,35; 16,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,4; 22,11</t>
+          <t>11,49; 22,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,6</t>
+          <t>9,09; 18,03</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 40,55</t>
+          <t>17,2; 40,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 40,25</t>
+          <t>16,29; 41,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 35,6</t>
+          <t>18,92; 35,95</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 19,76</t>
+          <t>8,19; 19,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,6</t>
+          <t>15,52; 25,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 20,97</t>
+          <t>12,83; 20,93</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3966</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2316; 8618</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2357; 11043</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19231</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32358</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6551; 20648</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13785; 26653</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22044; 43734</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12528</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24064</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7163; 17067</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7657; 19443</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16771; 31871</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62404</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>14685; 35344</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>28349; 47133</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>46438; 75764</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,04</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 55,01</t>
+          <t>13,69; 53,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 35,74</t>
+          <t>8,38; 34,83</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 16,86</t>
+          <t>5,0; 16,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 22,21</t>
+          <t>11,23; 21,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,03</t>
+          <t>8,49; 17,15</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 40,99</t>
+          <t>18,04; 41,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 41,35</t>
+          <t>15,62; 40,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 35,95</t>
+          <t>19,86; 36,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,71</t>
+          <t>8,51; 19,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,52; 25,8</t>
+          <t>15,04; 25,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,93</t>
+          <t>12,46; 20,86</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2316; 8618</t>
+          <t>2145; 8357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2357; 11043</t>
+          <t>2589; 10762</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6551; 20648</t>
+          <t>6123; 20701</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13785; 26653</t>
+          <t>13478; 26055</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22044; 43734</t>
+          <t>20599; 41597</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7163; 17067</t>
+          <t>7512; 17090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7657; 19443</t>
+          <t>7347; 19187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16771; 31871</t>
+          <t>17611; 32503</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14685; 35344</t>
+          <t>15258; 35624</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28349; 47133</t>
+          <t>27471; 46478</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46438; 75764</t>
+          <t>45122; 75508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,15</t>
+          <t>13,47; 59,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 53,34</t>
+          <t>0,0; 32,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 34,83</t>
+          <t>11,99; 41,73</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 16,9</t>
+          <t>10,96; 21,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,71</t>
+          <t>8,21; 19,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,15</t>
+          <t>10,6; 18,49</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 41,04</t>
+          <t>14,93; 40,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,62; 40,81</t>
+          <t>16,57; 39,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 36,66</t>
+          <t>18,48; 35,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,86</t>
+          <t>15,48; 25,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,44</t>
+          <t>12,06; 21,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,86</t>
+          <t>15,24; 22,41</t>
         </is>
       </c>
     </row>
@@ -774,18 +774,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>971</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5866</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>1876; 8287</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2145; 8357</t>
+          <t>0; 3211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2589; 10762</t>
+          <t>2843; 9891</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>29093</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6123; 20701</t>
+          <t>11829; 23525</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13478; 26055</t>
+          <t>7746; 18500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20599; 41597</t>
+          <t>21446; 37403</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>22550</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7512; 17090</t>
+          <t>6516; 17853</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7347; 19187</t>
+          <t>6716; 15838</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17611; 32503</t>
+          <t>15555; 29648</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15258; 35624</t>
+          <t>25608; 42931</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27471; 46478</t>
+          <t>17446; 31555</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45122; 75508</t>
+          <t>47256; 69490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A12_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>13,47; 59,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 32,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11,99; 41,73</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,96; 21,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,21; 19,61</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10,6; 18,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>27,02%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14,93; 40,9</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16,57; 39,08</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,48; 35,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15,48; 25,94</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 21,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,24; 22,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3516818290563118</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.09926160634579173</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2475156297463521</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4895</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5866</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1347421527880727</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1199351027720284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1876; 8287</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3211</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2843; 9891</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5953602986471208</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3283330938734136</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4173044265748136</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1562873279436737</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1296263050752842</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1438518481501087</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16865</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12228</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29093</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1096158128670193</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.08211302460092743</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1060401740573203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11829; 23525</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7746; 18500</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>21446; 37403</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2180029763929469</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1961097580611879</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1849383852443194</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.270160214143879</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2654613719266767</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.267897852518916</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11791</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10758</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22550</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1492897579487246</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1657064560452571</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1847977526099395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6516; 17853</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6716; 15838</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15555; 29648</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4090383034729868</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3908020708925551</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.352223954704227</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2027592191367933</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1656328339326856</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1854433406752149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>33552</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23957</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57510</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.154751667581097</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1206174450301799</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1523784629989432</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>25608; 42931</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17446; 31555</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>47256; 69490</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2594339984204225</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2181589745941018</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2240737278983316</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4895</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>971</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5866</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8287</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3211</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9891</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>16865</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>12228</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>29093</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11829</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>7746</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>21446</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>23525</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18500</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>37403</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>11791</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10758</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>22550</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>6516</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>6716</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>15555</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>17853</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>15838</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>29648</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>33552</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>23957</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>57510</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>25608</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>17446</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>47256</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>42931</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>31555</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>69490</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>